--- a/Data/FlightPlan/FPL_14SEP26.xlsx
+++ b/Data/FlightPlan/FPL_14SEP26.xlsx
@@ -155,148 +155,172 @@
     <t>08:30</t>
   </si>
   <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
     <t>11:20</t>
   </si>
   <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
   </si>
   <si>
     <t>07:30</t>
@@ -323,24 +347,6 @@
     <t>00:30</t>
   </si>
   <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
     <t>VN-A526</t>
   </si>
   <si>
@@ -674,9 +680,6 @@
     <t>08:20</t>
   </si>
   <si>
-    <t>10:35</t>
-  </si>
-  <si>
     <t>12:25</t>
   </si>
   <si>
@@ -1022,9 +1025,6 @@
     <t>VN-A657</t>
   </si>
   <si>
-    <t>17:40</t>
-  </si>
-  <si>
     <t>00:55</t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>Total Record(s): 390</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 14, 2026 03:14</t>
+    <t xml:space="preserve">Generated on  Sep 14, 2026 03:55</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2115,7 +2115,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="7">
-        <v>134</v>
+        <v>855</v>
       </c>
       <c t="s" r="C19" s="7">
         <v>14</v>
@@ -2131,24 +2131,28 @@
         <v>46</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c t="s" r="I19" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J19" s="7">
         <v>48</v>
       </c>
-      <c t="s" r="J19" s="7">
+      <c t="s" r="K19" s="7">
         <v>49</v>
       </c>
-      <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
+      <c t="s" r="M19" s="7">
+        <v>50</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c t="s" r="A20" s="6">
         <v>13</v>
       </c>
       <c r="B20" s="7">
-        <v>141</v>
+        <v>854</v>
       </c>
       <c t="s" r="C20" s="7">
         <v>14</v>
@@ -2161,7 +2165,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G20" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c t="s" r="H20" s="8">
         <v>46</v>
@@ -2172,9 +2176,13 @@
       <c t="s" r="J20" s="7">
         <v>51</v>
       </c>
-      <c r="K20" s="7"/>
+      <c t="s" r="K20" s="7">
+        <v>52</v>
+      </c>
       <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
+      <c t="s" r="M20" s="7">
+        <v>53</v>
+      </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c t="s" r="A21" s="6">
@@ -2197,13 +2205,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H21" s="8">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="I21" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2227,16 +2235,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G22" s="8">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="H22" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I22" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c t="s" r="J22" s="7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -2269,7 +2277,7 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
@@ -2281,10 +2289,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2302,7 +2310,7 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
@@ -2314,10 +2322,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2335,7 +2343,7 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
@@ -2350,7 +2358,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2368,7 +2376,7 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
@@ -2383,7 +2391,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2416,19 +2424,19 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="H29" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J29" s="7">
         <v>33</v>
@@ -2449,7 +2457,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2458,13 +2466,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2482,22 +2490,22 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="H31" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2515,7 +2523,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2524,10 +2532,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H32" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c t="s" r="J32" s="7">
         <v>47</v>
@@ -2563,22 +2571,22 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G34" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="H34" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2596,7 +2604,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2605,13 +2613,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2629,22 +2637,22 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2662,7 +2670,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2671,13 +2679,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2710,7 +2718,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2719,13 +2727,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2743,22 +2751,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H40" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2776,7 +2784,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2785,13 +2793,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I41" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2809,22 +2817,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2842,7 +2850,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2851,13 +2859,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2875,22 +2883,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2908,7 +2916,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2920,10 +2928,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2949,14 +2957,14 @@
         <v>13</v>
       </c>
       <c r="B47" s="7">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c t="s" r="C47" s="7">
         <v>14</v>
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -2968,10 +2976,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2982,14 +2990,14 @@
         <v>13</v>
       </c>
       <c r="B48" s="7">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c t="s" r="C48" s="7">
         <v>14</v>
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3001,10 +3009,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3015,14 +3023,14 @@
         <v>13</v>
       </c>
       <c r="B49" s="7">
-        <v>860</v>
+        <v>1805</v>
       </c>
       <c t="s" r="C49" s="7">
         <v>14</v>
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3031,50 +3039,46 @@
         <v>46</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>99</v>
-      </c>
-      <c t="s" r="K49" s="7">
         <v>100</v>
       </c>
+      <c r="K49" s="7"/>
       <c r="L49" s="7"/>
-      <c t="s" r="M49" s="7">
-        <v>101</v>
-      </c>
+      <c r="M49" s="7"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c t="s" r="A50" s="6">
         <v>13</v>
       </c>
       <c r="B50" s="7">
-        <v>861</v>
+        <v>1806</v>
       </c>
       <c t="s" r="C50" s="7">
         <v>14</v>
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I50" s="7">
+        <v>101</v>
+      </c>
+      <c t="s" r="J50" s="7">
         <v>102</v>
-      </c>
-      <c t="s" r="J50" s="7">
-        <v>103</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3100,29 +3104,29 @@
         <v>13</v>
       </c>
       <c r="B52" s="7">
-        <v>855</v>
+        <v>126</v>
       </c>
       <c t="s" r="C52" s="7">
         <v>14</v>
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
+        <v>103</v>
+      </c>
+      <c r="F52" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G52" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="H52" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I52" s="7">
         <v>104</v>
       </c>
-      <c r="F52" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G52" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H52" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I52" s="7">
-        <v>19</v>
-      </c>
       <c t="s" r="J52" s="7">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3133,29 +3137,29 @@
         <v>13</v>
       </c>
       <c r="B53" s="7">
-        <v>854</v>
+        <v>131</v>
       </c>
       <c t="s" r="C53" s="7">
         <v>14</v>
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3166,14 +3170,14 @@
         <v>13</v>
       </c>
       <c r="B54" s="7">
-        <v>1805</v>
+        <v>860</v>
       </c>
       <c t="s" r="C54" s="7">
         <v>14</v>
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3182,46 +3186,50 @@
         <v>46</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>107</v>
       </c>
-      <c r="K54" s="7"/>
+      <c t="s" r="K54" s="7">
+        <v>108</v>
+      </c>
       <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
+      <c t="s" r="M54" s="7">
+        <v>109</v>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c t="s" r="A55" s="6">
         <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>1806</v>
+        <v>861</v>
       </c>
       <c t="s" r="C55" s="7">
         <v>14</v>
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3254,22 +3262,22 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3287,7 +3295,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3296,13 +3304,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3335,22 +3343,22 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3368,22 +3376,22 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3401,22 +3409,22 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3434,7 +3442,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3443,10 +3451,10 @@
         <v>42</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>35</v>
@@ -3467,22 +3475,22 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H64" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3515,7 +3523,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3524,10 +3532,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>28</v>
@@ -3548,22 +3556,22 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3581,7 +3589,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3590,13 +3598,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3614,22 +3622,22 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3647,7 +3655,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3656,13 +3664,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3680,22 +3688,22 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3728,7 +3736,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3740,10 +3748,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3761,7 +3769,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3773,10 +3781,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3794,7 +3802,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3809,7 +3817,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3827,7 +3835,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3839,10 +3847,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3860,7 +3868,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3893,7 +3901,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3905,10 +3913,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3941,7 +3949,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3953,17 +3961,17 @@
         <v>46</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="K80" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -3978,7 +3986,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -3987,13 +3995,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4011,13 +4019,13 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>46</v>
@@ -4026,7 +4034,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4044,7 +4052,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4056,10 +4064,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4092,7 +4100,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4101,13 +4109,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4125,22 +4133,22 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4158,7 +4166,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4170,10 +4178,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4191,7 +4199,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4203,10 +4211,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4224,7 +4232,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4236,10 +4244,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4257,7 +4265,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4269,7 +4277,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>23</v>
@@ -4290,7 +4298,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4302,10 +4310,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4350,10 +4358,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4371,7 +4379,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4383,10 +4391,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4404,7 +4412,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4413,13 +4421,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4437,22 +4445,22 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4470,7 +4478,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4482,10 +4490,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4518,22 +4526,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4551,7 +4559,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4560,13 +4568,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4584,22 +4592,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4617,7 +4625,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4626,13 +4634,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4650,22 +4658,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4698,13 +4706,13 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>42</v>
@@ -4713,7 +4721,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4731,7 +4739,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4740,13 +4748,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I106" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4764,22 +4772,22 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4797,19 +4805,19 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>22</v>
@@ -4830,7 +4838,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4839,13 +4847,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4878,7 +4886,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4887,13 +4895,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4911,22 +4919,22 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4944,7 +4952,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4956,10 +4964,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -4977,7 +4985,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4989,10 +4997,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5025,7 +5033,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5034,13 +5042,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5058,19 +5066,19 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>37</v>
@@ -5091,7 +5099,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5100,13 +5108,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5139,22 +5147,22 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5172,22 +5180,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5205,22 +5213,22 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5238,22 +5246,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5286,22 +5294,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5319,7 +5327,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5328,13 +5336,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5352,13 +5360,13 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>30</v>
@@ -5367,7 +5375,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5400,22 +5408,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5433,7 +5441,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5445,10 +5453,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5466,7 +5474,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5478,10 +5486,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5499,7 +5507,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5508,13 +5516,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5532,13 +5540,13 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>46</v>
@@ -5547,7 +5555,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5576,11 +5584,11 @@
         <v>2925</v>
       </c>
       <c t="s" r="C135" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5589,13 +5597,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5613,22 +5621,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5646,7 +5654,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5658,10 +5666,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5679,7 +5687,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5691,10 +5699,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5712,7 +5720,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5721,13 +5729,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5756,26 +5764,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5789,11 +5797,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5805,10 +5813,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5826,7 +5834,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5835,16 +5843,16 @@
         <v>17</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
@@ -5863,22 +5871,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5896,22 +5904,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5929,22 +5937,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5977,7 +5985,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5989,10 +5997,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6010,7 +6018,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6019,13 +6027,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6043,22 +6051,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6091,7 +6099,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6100,13 +6108,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6124,22 +6132,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6157,7 +6165,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6169,10 +6177,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6190,7 +6198,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6202,10 +6210,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6238,22 +6246,22 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6271,7 +6279,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6280,13 +6288,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6319,7 +6327,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6328,13 +6336,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6352,22 +6360,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6385,7 +6393,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6394,13 +6402,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6418,22 +6426,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6466,7 +6474,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6475,13 +6483,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6499,13 +6507,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>46</v>
@@ -6514,7 +6522,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6532,7 +6540,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6541,13 +6549,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6565,22 +6573,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6613,7 +6621,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6625,10 +6633,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6646,7 +6654,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6655,13 +6663,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6679,19 +6687,19 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>34</v>
@@ -6712,7 +6720,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6721,13 +6729,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6745,19 +6753,19 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>35</v>
@@ -6778,7 +6786,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6787,10 +6795,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>37</v>
@@ -6811,22 +6819,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6859,7 +6867,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6868,13 +6876,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6892,22 +6900,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6925,7 +6933,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6934,13 +6942,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6958,22 +6966,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6991,7 +6999,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7000,13 +7008,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7024,22 +7032,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7072,22 +7080,22 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7105,7 +7113,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7114,13 +7122,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7138,22 +7146,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7171,22 +7179,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7204,22 +7212,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7237,22 +7245,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7294,13 +7302,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7318,22 +7326,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7351,7 +7359,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7360,13 +7368,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7384,22 +7392,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7417,7 +7425,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7426,13 +7434,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7450,22 +7458,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7483,7 +7491,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7495,10 +7503,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7516,7 +7524,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7528,10 +7536,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7564,7 +7572,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7573,13 +7581,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7597,22 +7605,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7630,7 +7638,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7642,10 +7650,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7663,7 +7671,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7675,10 +7683,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7696,7 +7704,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7705,13 +7713,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7729,22 +7737,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7762,7 +7770,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7774,7 +7782,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>40</v>
@@ -7810,7 +7818,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7819,13 +7827,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7843,22 +7851,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7876,7 +7884,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7888,10 +7896,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7909,7 +7917,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7921,10 +7929,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7942,7 +7950,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7954,7 +7962,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>22</v>
@@ -7990,7 +7998,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -7999,13 +8007,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8023,22 +8031,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8056,7 +8064,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8068,10 +8076,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8089,7 +8097,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8101,10 +8109,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8122,7 +8130,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8134,10 +8142,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8155,7 +8163,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8164,13 +8172,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8203,7 +8211,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8212,13 +8220,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8236,22 +8244,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8269,7 +8277,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8278,13 +8286,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8302,22 +8310,22 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8335,7 +8343,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8344,13 +8352,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8368,22 +8376,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8416,7 +8424,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8425,13 +8433,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8449,22 +8457,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8482,7 +8490,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8491,13 +8499,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8515,22 +8523,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8563,7 +8571,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8572,13 +8580,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8596,13 +8604,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>46</v>
@@ -8611,7 +8619,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8629,7 +8637,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8638,13 +8646,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8662,22 +8670,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8695,7 +8703,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8704,13 +8712,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8728,13 +8736,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>46</v>
@@ -8743,7 +8751,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8761,7 +8769,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8770,13 +8778,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8794,22 +8802,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8842,7 +8850,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8851,13 +8859,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8875,22 +8883,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8908,7 +8916,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8917,13 +8925,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8941,22 +8949,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8974,7 +8982,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -8983,13 +8991,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9007,22 +9015,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9055,7 +9063,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9064,13 +9072,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9088,22 +9096,22 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9121,7 +9129,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9133,10 +9141,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9154,7 +9162,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9166,10 +9174,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9187,7 +9195,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9199,10 +9207,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9235,7 +9243,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9244,13 +9252,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9268,22 +9276,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9301,7 +9309,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9310,13 +9318,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9334,22 +9342,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9382,7 +9390,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9391,13 +9399,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9415,22 +9423,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9448,22 +9456,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9481,22 +9489,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9529,7 +9537,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9541,10 +9549,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9562,7 +9570,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9571,10 +9579,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>33</v>
@@ -9595,13 +9603,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>30</v>
@@ -9610,7 +9618,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9628,7 +9636,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9637,13 +9645,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9661,22 +9669,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9709,7 +9717,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9718,13 +9726,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9742,22 +9750,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9775,7 +9783,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9787,10 +9795,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9808,7 +9816,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9823,7 +9831,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9841,7 +9849,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9850,13 +9858,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9874,22 +9882,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9907,7 +9915,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9916,13 +9924,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9940,22 +9948,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9988,7 +9996,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -9997,13 +10005,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10021,22 +10029,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10054,7 +10062,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10063,13 +10071,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10087,22 +10095,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10120,7 +10128,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10129,10 +10137,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>51</v>
@@ -10153,22 +10161,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10186,7 +10194,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10195,13 +10203,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10219,22 +10227,22 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10267,7 +10275,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10276,13 +10284,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10300,22 +10308,22 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10333,22 +10341,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10366,19 +10374,19 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>33</v>
@@ -10399,7 +10407,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10408,13 +10416,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10432,22 +10440,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10465,7 +10473,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10477,10 +10485,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10498,7 +10506,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10510,10 +10518,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10546,7 +10554,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10555,13 +10563,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10579,22 +10587,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10612,7 +10620,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10621,13 +10629,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10645,22 +10653,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10693,7 +10701,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10708,7 +10716,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10726,7 +10734,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10738,10 +10746,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10759,7 +10767,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10771,10 +10779,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10807,7 +10815,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10816,13 +10824,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10840,22 +10848,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10873,22 +10881,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10906,22 +10914,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10939,7 +10947,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10948,13 +10956,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10972,22 +10980,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11005,7 +11013,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11014,13 +11022,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11038,22 +11046,22 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11086,7 +11094,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11098,7 +11106,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>40</v>
@@ -11119,7 +11127,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11131,10 +11139,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11152,7 +11160,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11161,10 +11169,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>21</v>
@@ -11185,22 +11193,22 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11218,7 +11226,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11230,10 +11238,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>337</v>
+        <v>53</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11251,7 +11259,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11263,7 +11271,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>338</v>
@@ -11308,13 +11316,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11338,7 +11346,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>46</v>
@@ -11347,7 +11355,7 @@
         <v>340</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11377,10 +11385,10 @@
         <v>341</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11410,10 +11418,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11443,10 +11451,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11476,10 +11484,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11509,10 +11517,10 @@
         <v>341</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11542,10 +11550,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11590,10 +11598,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11623,10 +11631,10 @@
         <v>343</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11656,7 +11664,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>344</v>
@@ -11689,7 +11697,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>345</v>
@@ -11719,13 +11727,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11749,16 +11757,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11803,10 +11811,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11839,7 +11847,7 @@
         <v>347</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11866,13 +11874,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11896,16 +11904,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11986,7 +11994,7 @@
         <v>350</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12013,13 +12021,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12043,13 +12051,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>344</v>
@@ -12082,10 +12090,10 @@
         <v>351</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12115,10 +12123,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12148,10 +12156,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12196,10 +12204,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12226,13 +12234,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12256,7 +12264,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>46</v>
@@ -12265,7 +12273,7 @@
         <v>353</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12292,13 +12300,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12322,16 +12330,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12370,7 +12378,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>46</v>
@@ -12406,13 +12414,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12436,16 +12444,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12472,7 +12480,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>33</v>
@@ -12502,16 +12510,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12541,10 +12549,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12574,7 +12582,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>355</v>
@@ -12622,7 +12630,7 @@
         <v>351</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>19</v>
@@ -12655,10 +12663,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12685,13 +12693,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12715,7 +12723,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>46</v>
@@ -12724,7 +12732,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12751,13 +12759,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>345</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12781,16 +12789,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12835,10 +12843,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12865,13 +12873,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>337</v>
+        <v>53</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12895,16 +12903,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12946,13 +12954,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12976,16 +12984,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13033,7 +13041,7 @@
         <v>360</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13063,10 +13071,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13093,13 +13101,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>347</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13123,16 +13131,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13162,10 +13170,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13195,10 +13203,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13228,7 +13236,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>361</v>
@@ -13276,7 +13284,7 @@
         <v>351</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>18</v>
@@ -13312,7 +13320,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13339,13 +13347,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13369,16 +13377,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13408,7 +13416,7 @@
         <v>341</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>21</v>
@@ -13441,7 +13449,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>363</v>
@@ -13474,7 +13482,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>22</v>
@@ -13510,7 +13518,7 @@
         <v>365</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13555,10 +13563,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13585,13 +13593,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13615,16 +13623,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13651,13 +13659,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13681,13 +13689,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>367</v>
@@ -13732,13 +13740,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13762,16 +13770,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13801,10 +13809,10 @@
         <v>343</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13834,10 +13842,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13867,10 +13875,10 @@
         <v>369</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13900,10 +13908,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13948,10 +13956,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13981,10 +13989,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14014,10 +14022,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14047,10 +14055,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14095,10 +14103,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14125,13 +14133,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14155,16 +14163,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14188,16 +14196,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14239,10 +14247,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>373</v>
@@ -14269,16 +14277,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14308,10 +14316,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14341,10 +14349,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14371,13 +14379,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14401,16 +14409,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14458,7 +14466,7 @@
         <v>360</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14488,7 +14496,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>28</v>
@@ -14518,13 +14526,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14548,7 +14556,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>30</v>
@@ -14557,7 +14565,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14584,13 +14592,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14614,16 +14622,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>337</v>
+        <v>53</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14650,13 +14658,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14680,16 +14688,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14731,13 +14739,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14761,13 +14769,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>33</v>
@@ -14800,10 +14808,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14833,10 +14841,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14878,13 +14886,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14908,7 +14916,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>46</v>
@@ -14917,7 +14925,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14944,7 +14952,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I444" s="7">
         <v>23</v>
@@ -14992,13 +15000,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15022,16 +15030,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15061,10 +15069,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15094,10 +15102,10 @@
         <v>351</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15130,7 +15138,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15157,13 +15165,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I451" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15187,13 +15195,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>379</v>
@@ -15241,10 +15249,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15274,10 +15282,10 @@
         <v>381</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15307,7 +15315,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J456" s="7">
         <v>382</v>
@@ -15352,13 +15360,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15403,7 +15411,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J460" s="7">
         <v>363</v>
@@ -15433,13 +15441,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15468,7 +15476,7 @@
         <v>5805</v>
       </c>
       <c t="s" r="C463" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
@@ -15484,10 +15492,10 @@
         <v>387</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15501,7 +15509,7 @@
         <v>5806</v>
       </c>
       <c t="s" r="C464" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
@@ -15520,7 +15528,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15565,10 +15573,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -15598,10 +15606,10 @@
         <v>389</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -15646,10 +15654,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15679,10 +15687,10 @@
         <v>391</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15712,7 +15720,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>360</v>
@@ -15760,10 +15768,10 @@
         <v>393</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -15796,7 +15804,7 @@
         <v>394</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>

--- a/Data/FlightPlan/FPL_14SEP26.xlsx
+++ b/Data/FlightPlan/FPL_14SEP26.xlsx
@@ -551,6 +551,9 @@
     <t>12:55</t>
   </si>
   <si>
+    <t>14:14</t>
+  </si>
+  <si>
     <t>13:55</t>
   </si>
   <si>
@@ -575,6 +578,9 @@
     <t>VN-A544</t>
   </si>
   <si>
+    <t>08:51</t>
+  </si>
+  <si>
     <t>SIN</t>
   </si>
   <si>
@@ -758,345 +764,351 @@
     <t>VN-A629</t>
   </si>
   <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>07:18</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>06:59</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>07:58</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>10:43</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
     <t>10:30</t>
   </si>
   <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:52</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>06:38</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>08:22</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
     <t>15:10</t>
   </si>
   <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>07:18</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>06:54</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:59</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>07:58</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:52</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>06:38</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>08:22</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
     <t>VN-A663</t>
   </si>
   <si>
@@ -1178,7 +1190,7 @@
     <t>VN-A685</t>
   </si>
   <si>
-    <t>11:28</t>
+    <t>11:41</t>
   </si>
   <si>
     <t>VN-A687</t>
@@ -1190,9 +1202,6 @@
     <t>06:19</t>
   </si>
   <si>
-    <t>08:08</t>
-  </si>
-  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1211,7 +1220,7 @@
     <t>VN-A699</t>
   </si>
   <si>
-    <t>09:06</t>
+    <t>09:01</t>
   </si>
   <si>
     <t>23:20</t>
@@ -1268,7 +1277,7 @@
     <t>Total Record(s): 390</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 14, 2026 07:03</t>
+    <t xml:space="preserve">Generated on  Sep 14, 2026 07:29</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4690,7 +4699,9 @@
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
+      <c t="s" r="M101" s="7">
+        <v>180</v>
+      </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c t="s" r="A102" s="6">
@@ -4716,7 +4727,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>126</v>
@@ -4749,10 +4760,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4779,13 +4790,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4809,13 +4820,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>129</v>
@@ -4851,7 +4862,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4870,7 +4881,9 @@
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>189</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
@@ -4884,7 +4897,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4917,7 +4930,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4926,10 +4939,10 @@
         <v>96</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>72</v>
@@ -4950,13 +4963,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>47</v>
@@ -4983,7 +4996,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4995,7 +5008,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>99</v>
@@ -5031,7 +5044,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5043,10 +5056,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5064,7 +5077,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5076,10 +5089,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5097,7 +5110,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5109,10 +5122,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5130,7 +5143,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5142,10 +5155,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5178,7 +5191,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5211,7 +5224,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5244,7 +5257,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5259,7 +5272,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5292,7 +5305,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5307,7 +5320,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5325,7 +5338,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5340,7 +5353,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5358,7 +5371,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5373,7 +5386,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5391,7 +5404,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5403,7 +5416,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>164</v>
@@ -5439,7 +5452,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5454,7 +5467,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5472,7 +5485,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5484,7 +5497,7 @@
         <v>154</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>83</v>
@@ -5505,7 +5518,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5553,22 +5566,22 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5586,7 +5599,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5601,7 +5614,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5619,7 +5632,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5631,10 +5644,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5652,7 +5665,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5661,13 +5674,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5685,13 +5698,13 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>47</v>
@@ -5700,7 +5713,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5729,11 +5742,11 @@
         <v>2925</v>
       </c>
       <c t="s" r="C137" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5766,7 +5779,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5778,7 +5791,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>95</v>
@@ -5799,7 +5812,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5814,7 +5827,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5832,7 +5845,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5844,7 +5857,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>175</v>
@@ -5865,7 +5878,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5877,10 +5890,10 @@
         <v>117</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5909,31 +5922,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -5944,11 +5957,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5981,7 +5994,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5996,7 +6009,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="K145" s="7">
         <v>61</v>
@@ -6018,7 +6031,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6051,7 +6064,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6063,10 +6076,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6084,7 +6097,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6096,10 +6109,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6132,7 +6145,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6144,10 +6157,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6165,7 +6178,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6174,13 +6187,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6198,19 +6211,19 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>155</v>
@@ -6246,7 +6259,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6255,13 +6268,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I154" s="7">
         <v>160</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6279,22 +6292,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6312,7 +6325,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6327,7 +6340,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6345,7 +6358,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6357,10 +6370,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6393,13 +6406,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>47</v>
@@ -6426,7 +6439,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6438,7 +6451,7 @@
         <v>177</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>132</v>
@@ -6467,14 +6480,14 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>306</v>
+        <v>130</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6483,13 +6496,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>249</v>
+        <v>33</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6500,29 +6513,29 @@
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>305</v>
+        <v>775</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6533,78 +6546,78 @@
         <v>13</v>
       </c>
       <c r="B164" s="7">
-        <v>876</v>
+        <v>1601</v>
       </c>
       <c t="s" r="C164" s="7">
         <v>14</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>250</v>
+        <v>47</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>252</v>
+        <v>106</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
     </row>
     <row r="165" ht="15" customHeight="1">
-      <c t="s" r="A165" s="6">
-        <v>13</v>
-      </c>
-      <c r="B165" s="7">
-        <v>877</v>
-      </c>
-      <c t="s" r="C165" s="7">
-        <v>14</v>
-      </c>
+      <c r="A165" s="6"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
       <c r="D165" s="7"/>
-      <c t="s" r="E165" s="7">
-        <v>248</v>
-      </c>
-      <c r="F165" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G165" s="8">
-        <v>250</v>
-      </c>
-      <c t="s" r="H165" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I165" s="7">
-        <v>84</v>
-      </c>
-      <c t="s" r="J165" s="7">
-        <v>253</v>
-      </c>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="8"/>
+      <c r="H165" s="8"/>
+      <c r="I165" s="7"/>
+      <c r="J165" s="7"/>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c r="M165" s="7"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="6"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
+      <c t="s" r="A166" s="6">
+        <v>13</v>
+      </c>
+      <c r="B166" s="7">
+        <v>849</v>
+      </c>
+      <c t="s" r="C166" s="7">
+        <v>14</v>
+      </c>
       <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="8"/>
-      <c r="H166" s="8"/>
-      <c r="I166" s="7"/>
-      <c r="J166" s="7"/>
+      <c t="s" r="E166" s="7">
+        <v>253</v>
+      </c>
+      <c r="F166" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G166" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H166" s="8">
+        <v>254</v>
+      </c>
+      <c t="s" r="I166" s="7">
+        <v>132</v>
+      </c>
+      <c t="s" r="J166" s="7">
+        <v>179</v>
+      </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
@@ -6614,29 +6627,29 @@
         <v>13</v>
       </c>
       <c r="B167" s="7">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
+        <v>253</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
         <v>254</v>
       </c>
-      <c r="F167" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G167" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="H167" s="8">
-        <v>255</v>
+        <v>47</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6647,29 +6660,29 @@
         <v>13</v>
       </c>
       <c r="B168" s="7">
-        <v>848</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H168" s="8">
         <v>255</v>
       </c>
-      <c t="s" r="H168" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I168" s="7">
-        <v>35</v>
+        <v>256</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>164</v>
+        <v>257</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6677,81 +6690,81 @@
     </row>
     <row r="169" ht="14.25" customHeight="1">
       <c t="s" r="A169" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B169" s="7">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>47</v>
+        <v>255</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>256</v>
+        <v>47</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
     <row r="170" ht="15" customHeight="1">
-      <c t="s" r="A170" s="6">
-        <v>26</v>
-      </c>
-      <c r="B170" s="7">
-        <v>3909</v>
-      </c>
-      <c t="s" r="C170" s="7">
-        <v>14</v>
-      </c>
+      <c r="A170" s="6"/>
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
       <c r="D170" s="7"/>
-      <c t="s" r="E170" s="7">
-        <v>254</v>
-      </c>
-      <c r="F170" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G170" s="8">
-        <v>256</v>
-      </c>
-      <c t="s" r="H170" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I170" s="7">
-        <v>259</v>
-      </c>
-      <c t="s" r="J170" s="7">
-        <v>260</v>
-      </c>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="8"/>
+      <c r="H170" s="8"/>
+      <c r="I170" s="7"/>
+      <c r="J170" s="7"/>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="6"/>
-      <c r="B171" s="7"/>
-      <c r="C171" s="7"/>
+      <c t="s" r="A171" s="6">
+        <v>13</v>
+      </c>
+      <c r="B171" s="7">
+        <v>125</v>
+      </c>
+      <c t="s" r="C171" s="7">
+        <v>14</v>
+      </c>
       <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
-      <c r="G171" s="8"/>
-      <c r="H171" s="8"/>
-      <c r="I171" s="7"/>
-      <c r="J171" s="7"/>
+      <c t="s" r="E171" s="7">
+        <v>260</v>
+      </c>
+      <c r="F171" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G171" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H171" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I171" s="7">
+        <v>261</v>
+      </c>
+      <c t="s" r="J171" s="7">
+        <v>171</v>
+      </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
@@ -6761,29 +6774,29 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>125</v>
+        <v>634</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c t="s" r="I172" s="7">
         <v>262</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6794,29 +6807,29 @@
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>634</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>264</v>
+        <v>35</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6827,29 +6840,29 @@
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H174" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H174" s="8">
-        <v>31</v>
-      </c>
       <c t="s" r="I174" s="7">
-        <v>265</v>
+        <v>63</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6860,29 +6873,29 @@
         <v>13</v>
       </c>
       <c r="B175" s="7">
-        <v>1505</v>
+        <v>512</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>14</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H175" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H175" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I175" s="7">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6893,29 +6906,29 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H176" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H176" s="8">
-        <v>31</v>
-      </c>
       <c t="s" r="I176" s="7">
-        <v>72</v>
+        <v>239</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6926,145 +6939,145 @@
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H177" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H177" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I177" s="7">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>38</v>
+        <v>266</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c r="M177" s="7"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c t="s" r="A178" s="6">
-        <v>13</v>
-      </c>
-      <c r="B178" s="7">
-        <v>518</v>
-      </c>
-      <c t="s" r="C178" s="7">
-        <v>14</v>
-      </c>
+      <c r="A178" s="6"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
       <c r="D178" s="7"/>
-      <c t="s" r="E178" s="7">
-        <v>261</v>
-      </c>
-      <c r="F178" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G178" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="H178" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I178" s="7">
-        <v>266</v>
-      </c>
-      <c t="s" r="J178" s="7">
-        <v>267</v>
-      </c>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="8"/>
+      <c r="H178" s="8"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="7"/>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c r="M178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c r="A179" s="6"/>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
+      <c t="s" r="A179" s="6">
+        <v>13</v>
+      </c>
+      <c r="B179" s="7">
+        <v>350</v>
+      </c>
+      <c t="s" r="C179" s="7">
+        <v>14</v>
+      </c>
       <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-      <c r="G179" s="8"/>
-      <c r="H179" s="8"/>
-      <c r="I179" s="7"/>
-      <c r="J179" s="7"/>
+      <c t="s" r="E179" s="7">
+        <v>267</v>
+      </c>
+      <c r="F179" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G179" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H179" s="8">
+        <v>73</v>
+      </c>
+      <c t="s" r="I179" s="7">
+        <v>108</v>
+      </c>
+      <c t="s" r="J179" s="7">
+        <v>110</v>
+      </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
-      <c r="M179" s="7"/>
+      <c t="s" r="M179" s="7">
+        <v>268</v>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c t="s" r="A180" s="6">
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
-      <c t="s" r="M180" s="7">
-        <v>269</v>
-      </c>
+      <c r="M180" s="7"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>351</v>
+        <v>852</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7075,29 +7088,29 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7108,29 +7121,29 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>47</v>
+        <v>269</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>83</v>
+        <v>270</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7138,148 +7151,148 @@
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c t="s" r="A184" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B184" s="7">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>47</v>
+        <v>269</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>270</v>
+        <v>47</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>148</v>
+        <v>271</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c t="s" r="A185" s="6">
-        <v>26</v>
-      </c>
-      <c r="B185" s="7">
-        <v>859</v>
-      </c>
-      <c t="s" r="C185" s="7">
-        <v>14</v>
-      </c>
+      <c r="A185" s="6"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="7"/>
       <c r="D185" s="7"/>
-      <c t="s" r="E185" s="7">
-        <v>268</v>
-      </c>
-      <c r="F185" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G185" s="8">
-        <v>270</v>
-      </c>
-      <c t="s" r="H185" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I185" s="7">
-        <v>272</v>
-      </c>
-      <c t="s" r="J185" s="7">
-        <v>273</v>
-      </c>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7"/>
+      <c r="G185" s="8"/>
+      <c r="H185" s="8"/>
+      <c r="I185" s="7"/>
+      <c r="J185" s="7"/>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="6"/>
-      <c r="B186" s="7"/>
-      <c r="C186" s="7"/>
+      <c t="s" r="A186" s="6">
+        <v>13</v>
+      </c>
+      <c r="B186" s="7">
+        <v>621</v>
+      </c>
+      <c t="s" r="C186" s="7">
+        <v>14</v>
+      </c>
       <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
-      <c r="G186" s="8"/>
-      <c r="H186" s="8"/>
-      <c r="I186" s="7"/>
-      <c r="J186" s="7"/>
+      <c t="s" r="E186" s="7">
+        <v>273</v>
+      </c>
+      <c r="F186" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G186" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H186" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I186" s="7">
+        <v>247</v>
+      </c>
+      <c t="s" r="J186" s="7">
+        <v>261</v>
+      </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
-      <c r="M186" s="7"/>
+      <c t="s" r="M186" s="7">
+        <v>274</v>
+      </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c t="s" r="A187" s="6">
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H187" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H187" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I187" s="7">
-        <v>245</v>
+        <v>110</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
-      <c t="s" r="M187" s="7">
-        <v>275</v>
-      </c>
+      <c r="M187" s="7"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c t="s" r="A188" s="6">
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>632</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7290,29 +7303,29 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>8890</v>
+        <v>8891</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
+        <v>275</v>
+      </c>
+      <c t="s" r="H189" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H189" s="8">
+      <c t="s" r="I189" s="7">
         <v>276</v>
       </c>
-      <c t="s" r="I189" s="7">
-        <v>195</v>
-      </c>
       <c t="s" r="J189" s="7">
-        <v>204</v>
+        <v>277</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7323,29 +7336,29 @@
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>8891</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>276</v>
+        <v>96</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>277</v>
+        <v>36</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7356,145 +7369,145 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>8892</v>
+        <v>8893</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
+        <v>275</v>
+      </c>
+      <c t="s" r="H191" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H191" s="8">
-        <v>276</v>
-      </c>
       <c t="s" r="I191" s="7">
-        <v>36</v>
+        <v>278</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c t="s" r="A192" s="6">
-        <v>13</v>
-      </c>
-      <c r="B192" s="7">
-        <v>8893</v>
-      </c>
-      <c t="s" r="C192" s="7">
-        <v>14</v>
-      </c>
+      <c r="A192" s="6"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
       <c r="D192" s="7"/>
-      <c t="s" r="E192" s="7">
-        <v>274</v>
-      </c>
-      <c r="F192" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G192" s="8">
-        <v>276</v>
-      </c>
-      <c t="s" r="H192" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="I192" s="7">
-        <v>279</v>
-      </c>
-      <c t="s" r="J192" s="7">
-        <v>167</v>
-      </c>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
-      <c r="A193" s="6"/>
-      <c r="B193" s="7"/>
-      <c r="C193" s="7"/>
+      <c t="s" r="A193" s="6">
+        <v>13</v>
+      </c>
+      <c r="B193" s="7">
+        <v>501</v>
+      </c>
+      <c t="s" r="C193" s="7">
+        <v>14</v>
+      </c>
       <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-      <c r="G193" s="8"/>
-      <c r="H193" s="8"/>
-      <c r="I193" s="7"/>
-      <c r="J193" s="7"/>
+      <c t="s" r="E193" s="7">
+        <v>279</v>
+      </c>
+      <c r="F193" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G193" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H193" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I193" s="7">
+        <v>280</v>
+      </c>
+      <c t="s" r="J193" s="7">
+        <v>261</v>
+      </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
-      <c r="M193" s="7"/>
+      <c t="s" r="M193" s="7">
+        <v>281</v>
+      </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c t="s" r="A194" s="6">
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H194" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H194" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I194" s="7">
-        <v>281</v>
+        <v>110</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
-      <c t="s" r="M194" s="7">
-        <v>282</v>
-      </c>
+      <c r="M194" s="7"/>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c t="s" r="A195" s="6">
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>514</v>
+        <v>563</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7505,29 +7518,29 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
+        <v>92</v>
+      </c>
+      <c t="s" r="H196" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H196" s="8">
-        <v>92</v>
-      </c>
       <c t="s" r="I196" s="7">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7538,29 +7551,29 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>564</v>
+        <v>407</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7571,29 +7584,29 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
+        <v>69</v>
+      </c>
+      <c t="s" r="H198" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H198" s="8">
-        <v>69</v>
-      </c>
       <c t="s" r="I198" s="7">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7604,29 +7617,29 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>408</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7637,78 +7650,78 @@
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H200" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H200" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I200" s="7">
-        <v>76</v>
+        <v>282</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>218</v>
+        <v>283</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c t="s" r="A201" s="6">
-        <v>13</v>
-      </c>
-      <c r="B201" s="7">
-        <v>1128</v>
-      </c>
-      <c t="s" r="C201" s="7">
-        <v>14</v>
-      </c>
+      <c r="A201" s="6"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="7"/>
       <c r="D201" s="7"/>
-      <c t="s" r="E201" s="7">
-        <v>280</v>
-      </c>
-      <c r="F201" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G201" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H201" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I201" s="7">
-        <v>283</v>
-      </c>
-      <c t="s" r="J201" s="7">
-        <v>284</v>
-      </c>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="8"/>
+      <c r="H201" s="8"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="7"/>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="6"/>
-      <c r="B202" s="7"/>
-      <c r="C202" s="7"/>
+      <c t="s" r="A202" s="6">
+        <v>13</v>
+      </c>
+      <c r="B202" s="7">
+        <v>421</v>
+      </c>
+      <c t="s" r="C202" s="7">
+        <v>14</v>
+      </c>
       <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
-      <c r="G202" s="8"/>
-      <c r="H202" s="8"/>
-      <c r="I202" s="7"/>
-      <c r="J202" s="7"/>
+      <c t="s" r="E202" s="7">
+        <v>284</v>
+      </c>
+      <c r="F202" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G202" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H202" s="8">
+        <v>285</v>
+      </c>
+      <c t="s" r="I202" s="7">
+        <v>41</v>
+      </c>
+      <c t="s" r="J202" s="7">
+        <v>152</v>
+      </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
@@ -7718,29 +7731,29 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
+        <v>284</v>
+      </c>
+      <c r="F203" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G203" s="8">
         <v>285</v>
       </c>
-      <c r="F203" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G203" s="8">
+      <c t="s" r="H203" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H203" s="8">
+      <c t="s" r="I203" s="7">
         <v>286</v>
       </c>
-      <c t="s" r="I203" s="7">
-        <v>41</v>
-      </c>
       <c t="s" r="J203" s="7">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7751,29 +7764,29 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>286</v>
+        <v>31</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>287</v>
+        <v>123</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7784,29 +7797,29 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
+        <v>43</v>
+      </c>
+      <c t="s" r="H205" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H205" s="8">
-        <v>43</v>
-      </c>
       <c t="s" r="I205" s="7">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7817,26 +7830,26 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>288</v>
@@ -7850,29 +7863,29 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
+        <v>73</v>
+      </c>
+      <c t="s" r="H207" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H207" s="8">
-        <v>73</v>
-      </c>
       <c t="s" r="I207" s="7">
-        <v>173</v>
+        <v>289</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7880,81 +7893,81 @@
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c t="s" r="A208" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B208" s="7">
-        <v>496</v>
+        <v>982</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>253</v>
+        <v>41</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c r="M208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c t="s" r="A209" s="6">
-        <v>26</v>
-      </c>
-      <c r="B209" s="7">
-        <v>982</v>
-      </c>
-      <c t="s" r="C209" s="7">
-        <v>14</v>
-      </c>
+      <c r="A209" s="6"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="7"/>
       <c r="D209" s="7"/>
-      <c t="s" r="E209" s="7">
-        <v>285</v>
-      </c>
-      <c r="F209" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G209" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H209" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I209" s="7">
-        <v>291</v>
-      </c>
-      <c t="s" r="J209" s="7">
-        <v>41</v>
-      </c>
+      <c r="E209" s="7"/>
+      <c r="F209" s="7"/>
+      <c r="G209" s="8"/>
+      <c r="H209" s="8"/>
+      <c r="I209" s="7"/>
+      <c r="J209" s="7"/>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="6"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
+      <c t="s" r="A210" s="6">
+        <v>13</v>
+      </c>
+      <c r="B210" s="7">
+        <v>503</v>
+      </c>
+      <c t="s" r="C210" s="7">
+        <v>14</v>
+      </c>
       <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-      <c r="G210" s="8"/>
-      <c r="H210" s="8"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
+      <c t="s" r="E210" s="7">
+        <v>292</v>
+      </c>
+      <c r="F210" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G210" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H210" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I210" s="7">
+        <v>110</v>
+      </c>
+      <c t="s" r="J210" s="7">
+        <v>160</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
@@ -7964,7 +7977,7 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
@@ -7977,16 +7990,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H211" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H211" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I211" s="7">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>160</v>
+        <v>293</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7997,7 +8010,7 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>524</v>
+        <v>133</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
@@ -8010,16 +8023,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>293</v>
+        <v>51</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8030,7 +8043,7 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
@@ -8043,16 +8056,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H213" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H213" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I213" s="7">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>51</v>
+        <v>216</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8063,7 +8076,7 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
@@ -8076,75 +8089,77 @@
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>214</v>
+        <v>23</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c t="s" r="A215" s="6">
-        <v>13</v>
-      </c>
-      <c r="B215" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="C215" s="7">
-        <v>14</v>
-      </c>
+      <c r="A215" s="6"/>
+      <c r="B215" s="7"/>
+      <c r="C215" s="7"/>
       <c r="D215" s="7"/>
-      <c t="s" r="E215" s="7">
-        <v>292</v>
-      </c>
-      <c r="F215" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G215" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H215" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I215" s="7">
-        <v>164</v>
-      </c>
-      <c t="s" r="J215" s="7">
-        <v>23</v>
-      </c>
+      <c r="E215" s="7"/>
+      <c r="F215" s="7"/>
+      <c r="G215" s="8"/>
+      <c r="H215" s="8"/>
+      <c r="I215" s="7"/>
+      <c r="J215" s="7"/>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
-      <c r="A216" s="6"/>
-      <c r="B216" s="7"/>
-      <c r="C216" s="7"/>
+      <c t="s" r="A216" s="6">
+        <v>13</v>
+      </c>
+      <c r="B216" s="7">
+        <v>925</v>
+      </c>
+      <c t="s" r="C216" s="7">
+        <v>14</v>
+      </c>
       <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
-      <c r="F216" s="7"/>
-      <c r="G216" s="8"/>
-      <c r="H216" s="8"/>
-      <c r="I216" s="7"/>
-      <c r="J216" s="7"/>
+      <c t="s" r="E216" s="7">
+        <v>294</v>
+      </c>
+      <c r="F216" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G216" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H216" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I216" s="7">
+        <v>46</v>
+      </c>
+      <c t="s" r="J216" s="7">
+        <v>295</v>
+      </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
-      <c r="M216" s="7"/>
+      <c t="s" r="M216" s="7">
+        <v>111</v>
+      </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>925</v>
+        <v>731</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
@@ -8157,29 +8172,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>46</v>
+        <v>179</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
-      <c t="s" r="M217" s="7">
-        <v>111</v>
-      </c>
+      <c r="M217" s="7"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c t="s" r="A218" s="6">
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>731</v>
+        <v>772</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
@@ -8192,16 +8205,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8212,7 +8225,7 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>772</v>
+        <v>441</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
@@ -8225,16 +8238,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>205</v>
+        <v>298</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8245,7 +8258,7 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
@@ -8258,16 +8271,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
+        <v>43</v>
+      </c>
+      <c t="s" r="H220" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H220" s="8">
-        <v>43</v>
-      </c>
       <c t="s" r="I220" s="7">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8275,10 +8288,10 @@
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c t="s" r="A221" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B221" s="7">
-        <v>442</v>
+        <v>958</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
@@ -8291,75 +8304,77 @@
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>31</v>
+        <v>300</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>299</v>
+        <v>132</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c t="s" r="A222" s="6">
-        <v>26</v>
-      </c>
-      <c r="B222" s="7">
-        <v>958</v>
-      </c>
-      <c t="s" r="C222" s="7">
-        <v>14</v>
-      </c>
+      <c r="A222" s="6"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="7"/>
       <c r="D222" s="7"/>
-      <c t="s" r="E222" s="7">
-        <v>294</v>
-      </c>
-      <c r="F222" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G222" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H222" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="I222" s="7">
-        <v>301</v>
-      </c>
-      <c t="s" r="J222" s="7">
-        <v>132</v>
-      </c>
+      <c r="E222" s="7"/>
+      <c r="F222" s="7"/>
+      <c r="G222" s="8"/>
+      <c r="H222" s="8"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="7"/>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
-      <c r="A223" s="6"/>
-      <c r="B223" s="7"/>
-      <c r="C223" s="7"/>
+      <c t="s" r="A223" s="6">
+        <v>13</v>
+      </c>
+      <c r="B223" s="7">
+        <v>270</v>
+      </c>
+      <c t="s" r="C223" s="7">
+        <v>14</v>
+      </c>
       <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
-      <c r="F223" s="7"/>
-      <c r="G223" s="8"/>
-      <c r="H223" s="8"/>
-      <c r="I223" s="7"/>
-      <c r="J223" s="7"/>
+      <c t="s" r="E223" s="7">
+        <v>302</v>
+      </c>
+      <c r="F223" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G223" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H223" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I223" s="7">
+        <v>142</v>
+      </c>
+      <c t="s" r="J223" s="7">
+        <v>110</v>
+      </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>303</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
@@ -8372,29 +8387,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>110</v>
+        <v>304</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
-      <c t="s" r="M224" s="7">
-        <v>303</v>
-      </c>
+      <c r="M224" s="7"/>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c t="s" r="A225" s="6">
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
@@ -8407,16 +8420,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>304</v>
+        <v>214</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8427,7 +8440,7 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
@@ -8440,16 +8453,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>263</v>
+        <v>124</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>212</v>
+        <v>305</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8460,7 +8473,7 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>245</v>
+        <v>394</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
@@ -8473,16 +8486,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>47</v>
+        <v>285</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8493,7 +8506,7 @@
         <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
@@ -8506,65 +8519,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>47</v>
+        <v>285</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>286</v>
+        <v>47</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>298</v>
+        <v>219</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c t="s" r="A229" s="6">
-        <v>13</v>
-      </c>
-      <c r="B229" s="7">
-        <v>395</v>
-      </c>
-      <c t="s" r="C229" s="7">
-        <v>14</v>
-      </c>
+      <c r="A229" s="6"/>
+      <c r="B229" s="7"/>
+      <c r="C229" s="7"/>
       <c r="D229" s="7"/>
-      <c t="s" r="E229" s="7">
-        <v>302</v>
-      </c>
-      <c r="F229" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G229" s="8">
-        <v>286</v>
-      </c>
-      <c t="s" r="H229" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I229" s="7">
-        <v>166</v>
-      </c>
-      <c t="s" r="J229" s="7">
-        <v>217</v>
-      </c>
+      <c r="E229" s="7"/>
+      <c r="F229" s="7"/>
+      <c r="G229" s="8"/>
+      <c r="H229" s="8"/>
+      <c r="I229" s="7"/>
+      <c r="J229" s="7"/>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="6"/>
-      <c r="B230" s="7"/>
-      <c r="C230" s="7"/>
+      <c t="s" r="A230" s="6">
+        <v>13</v>
+      </c>
+      <c r="B230" s="7">
+        <v>811</v>
+      </c>
+      <c t="s" r="C230" s="7">
+        <v>14</v>
+      </c>
       <c r="D230" s="7"/>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
-      <c r="G230" s="8"/>
-      <c r="H230" s="8"/>
-      <c r="I230" s="7"/>
-      <c r="J230" s="7"/>
+      <c t="s" r="E230" s="7">
+        <v>306</v>
+      </c>
+      <c r="F230" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G230" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H230" s="8">
+        <v>190</v>
+      </c>
+      <c t="s" r="I230" s="7">
+        <v>89</v>
+      </c>
+      <c t="s" r="J230" s="7">
+        <v>263</v>
+      </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c r="M230" s="7"/>
@@ -8574,7 +8587,7 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>811</v>
+        <v>984</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
@@ -8587,16 +8600,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>89</v>
+        <v>209</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>264</v>
+        <v>307</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8607,7 +8620,7 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
@@ -8620,16 +8633,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>43</v>
+        <v>190</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>207</v>
+        <v>308</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8640,7 +8653,7 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>983</v>
+        <v>812</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
@@ -8653,75 +8666,77 @@
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>43</v>
+        <v>190</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>308</v>
+        <v>219</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c t="s" r="A234" s="6">
-        <v>13</v>
-      </c>
-      <c r="B234" s="7">
-        <v>812</v>
-      </c>
-      <c t="s" r="C234" s="7">
-        <v>14</v>
-      </c>
+      <c r="A234" s="6"/>
+      <c r="B234" s="7"/>
+      <c r="C234" s="7"/>
       <c r="D234" s="7"/>
-      <c t="s" r="E234" s="7">
-        <v>306</v>
-      </c>
-      <c r="F234" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G234" s="8">
-        <v>188</v>
-      </c>
-      <c t="s" r="H234" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I234" s="7">
-        <v>217</v>
-      </c>
-      <c t="s" r="J234" s="7">
-        <v>98</v>
-      </c>
+      <c r="E234" s="7"/>
+      <c r="F234" s="7"/>
+      <c r="G234" s="8"/>
+      <c r="H234" s="8"/>
+      <c r="I234" s="7"/>
+      <c r="J234" s="7"/>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="6"/>
-      <c r="B235" s="7"/>
-      <c r="C235" s="7"/>
+      <c t="s" r="A235" s="6">
+        <v>13</v>
+      </c>
+      <c r="B235" s="7">
+        <v>260</v>
+      </c>
+      <c t="s" r="C235" s="7">
+        <v>14</v>
+      </c>
       <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
-      <c r="F235" s="7"/>
-      <c r="G235" s="8"/>
-      <c r="H235" s="8"/>
-      <c r="I235" s="7"/>
-      <c r="J235" s="7"/>
+      <c t="s" r="E235" s="7">
+        <v>309</v>
+      </c>
+      <c r="F235" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G235" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H235" s="8">
+        <v>218</v>
+      </c>
+      <c t="s" r="I235" s="7">
+        <v>310</v>
+      </c>
+      <c t="s" r="J235" s="7">
+        <v>150</v>
+      </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
-      <c r="M235" s="7"/>
+      <c t="s" r="M235" s="7">
+        <v>311</v>
+      </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
       <c t="s" r="A236" s="6">
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
@@ -8734,29 +8749,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>310</v>
+        <v>33</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>150</v>
+        <v>312</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
-      <c t="s" r="M236" s="7">
-        <v>311</v>
-      </c>
+      <c r="M236" s="7"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c t="s" r="A237" s="6">
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>261</v>
+        <v>803</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
@@ -8769,16 +8782,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>312</v>
+        <v>214</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8789,7 +8802,7 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
@@ -8802,16 +8815,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8822,7 +8835,7 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>804</v>
+        <v>310</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
@@ -8835,16 +8848,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8855,7 +8868,7 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
@@ -8868,16 +8881,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>214</v>
+        <v>36</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>147</v>
+        <v>313</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8888,7 +8901,7 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>309</v>
+        <v>652</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
@@ -8901,16 +8914,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>36</v>
+        <v>314</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8921,7 +8934,7 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
@@ -8934,65 +8947,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>314</v>
+        <v>100</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c t="s" r="A243" s="6">
-        <v>13</v>
-      </c>
-      <c r="B243" s="7">
-        <v>631</v>
-      </c>
-      <c t="s" r="C243" s="7">
-        <v>14</v>
-      </c>
+      <c r="A243" s="6"/>
+      <c r="B243" s="7"/>
+      <c r="C243" s="7"/>
       <c r="D243" s="7"/>
-      <c t="s" r="E243" s="7">
-        <v>309</v>
-      </c>
-      <c r="F243" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G243" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="H243" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I243" s="7">
-        <v>100</v>
-      </c>
-      <c t="s" r="J243" s="7">
-        <v>315</v>
-      </c>
+      <c r="E243" s="7"/>
+      <c r="F243" s="7"/>
+      <c r="G243" s="8"/>
+      <c r="H243" s="8"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="7"/>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="6"/>
-      <c r="B244" s="7"/>
-      <c r="C244" s="7"/>
+      <c t="s" r="A244" s="6">
+        <v>13</v>
+      </c>
+      <c r="B244" s="7">
+        <v>274</v>
+      </c>
+      <c t="s" r="C244" s="7">
+        <v>14</v>
+      </c>
       <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-      <c r="G244" s="8"/>
-      <c r="H244" s="8"/>
-      <c r="I244" s="7"/>
-      <c r="J244" s="7"/>
+      <c t="s" r="E244" s="7">
+        <v>316</v>
+      </c>
+      <c r="F244" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G244" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H244" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I244" s="7">
+        <v>304</v>
+      </c>
+      <c t="s" r="J244" s="7">
+        <v>162</v>
+      </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
@@ -9002,7 +9015,7 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
@@ -9015,16 +9028,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>304</v>
+        <v>49</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>162</v>
+        <v>53</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9035,7 +9048,7 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
@@ -9048,16 +9061,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H246" s="8">
         <v>88</v>
       </c>
-      <c t="s" r="H246" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I246" s="7">
-        <v>49</v>
+        <v>305</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9068,7 +9081,7 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
@@ -9081,16 +9094,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>305</v>
+        <v>147</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>198</v>
+        <v>289</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9101,7 +9114,7 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>281</v>
+        <v>1282</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
@@ -9114,16 +9127,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H248" s="8">
         <v>88</v>
       </c>
-      <c t="s" r="H248" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I248" s="7">
-        <v>147</v>
+        <v>224</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9134,7 +9147,7 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>1282</v>
+        <v>926</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
@@ -9147,65 +9160,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>222</v>
+        <v>317</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c t="s" r="A250" s="6">
-        <v>13</v>
-      </c>
-      <c r="B250" s="7">
-        <v>926</v>
-      </c>
-      <c t="s" r="C250" s="7">
-        <v>14</v>
-      </c>
+      <c r="A250" s="6"/>
+      <c r="B250" s="7"/>
+      <c r="C250" s="7"/>
       <c r="D250" s="7"/>
-      <c t="s" r="E250" s="7">
-        <v>316</v>
-      </c>
-      <c r="F250" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G250" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="H250" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I250" s="7">
-        <v>317</v>
-      </c>
-      <c t="s" r="J250" s="7">
-        <v>318</v>
-      </c>
+      <c r="E250" s="7"/>
+      <c r="F250" s="7"/>
+      <c r="G250" s="8"/>
+      <c r="H250" s="8"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="7"/>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="6"/>
-      <c r="B251" s="7"/>
-      <c r="C251" s="7"/>
+      <c t="s" r="A251" s="6">
+        <v>13</v>
+      </c>
+      <c r="B251" s="7">
+        <v>507</v>
+      </c>
+      <c t="s" r="C251" s="7">
+        <v>14</v>
+      </c>
       <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
-      <c r="F251" s="7"/>
-      <c r="G251" s="8"/>
-      <c r="H251" s="8"/>
-      <c r="I251" s="7"/>
-      <c r="J251" s="7"/>
+      <c t="s" r="E251" s="7">
+        <v>319</v>
+      </c>
+      <c r="F251" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G251" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H251" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I251" s="7">
+        <v>61</v>
+      </c>
+      <c t="s" r="J251" s="7">
+        <v>49</v>
+      </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
@@ -9215,7 +9228,7 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
@@ -9228,16 +9241,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H252" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H252" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I252" s="7">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9248,7 +9261,7 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>508</v>
+        <v>773</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
@@ -9261,16 +9274,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9281,7 +9294,7 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
@@ -9294,16 +9307,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H254" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H254" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I254" s="7">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>298</v>
+        <v>233</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9314,7 +9327,7 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>776</v>
+        <v>962</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
@@ -9327,65 +9340,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>166</v>
+        <v>320</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>231</v>
+        <v>142</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c t="s" r="A256" s="6">
-        <v>13</v>
-      </c>
-      <c r="B256" s="7">
-        <v>962</v>
-      </c>
-      <c t="s" r="C256" s="7">
-        <v>14</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c t="s" r="E256" s="7">
-        <v>319</v>
-      </c>
-      <c r="F256" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I256" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="J256" s="7">
-        <v>142</v>
-      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
-      <c r="A257" s="6"/>
-      <c r="B257" s="7"/>
-      <c r="C257" s="7"/>
+      <c t="s" r="A257" s="6">
+        <v>13</v>
+      </c>
+      <c r="B257" s="7">
+        <v>893</v>
+      </c>
+      <c t="s" r="C257" s="7">
+        <v>14</v>
+      </c>
       <c r="D257" s="7"/>
-      <c r="E257" s="7"/>
-      <c r="F257" s="7"/>
-      <c r="G257" s="8"/>
-      <c r="H257" s="8"/>
-      <c r="I257" s="7"/>
-      <c r="J257" s="7"/>
+      <c t="s" r="E257" s="7">
+        <v>321</v>
+      </c>
+      <c r="F257" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G257" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H257" s="8">
+        <v>254</v>
+      </c>
+      <c t="s" r="I257" s="7">
+        <v>152</v>
+      </c>
+      <c t="s" r="J257" s="7">
+        <v>251</v>
+      </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c r="M257" s="7"/>
@@ -9395,7 +9408,7 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
@@ -9408,16 +9421,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>47</v>
+        <v>254</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>255</v>
+        <v>47</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>322</v>
+        <v>217</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9428,7 +9441,7 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
@@ -9441,16 +9454,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>255</v>
+        <v>47</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>47</v>
+        <v>322</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9458,10 +9471,10 @@
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B260" s="7">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
@@ -9474,97 +9487,99 @@
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>47</v>
+        <v>322</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>323</v>
+        <v>47</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c t="s" r="A261" s="6">
-        <v>26</v>
-      </c>
-      <c r="B261" s="7">
-        <v>896</v>
-      </c>
-      <c t="s" r="C261" s="7">
-        <v>14</v>
-      </c>
+      <c r="A261" s="6"/>
+      <c r="B261" s="7"/>
+      <c r="C261" s="7"/>
       <c r="D261" s="7"/>
-      <c t="s" r="E261" s="7">
-        <v>321</v>
-      </c>
-      <c r="F261" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G261" s="8">
-        <v>323</v>
-      </c>
-      <c t="s" r="H261" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I261" s="7">
-        <v>156</v>
-      </c>
-      <c t="s" r="J261" s="7">
-        <v>310</v>
-      </c>
+      <c r="E261" s="7"/>
+      <c r="F261" s="7"/>
+      <c r="G261" s="8"/>
+      <c r="H261" s="8"/>
+      <c r="I261" s="7"/>
+      <c r="J261" s="7"/>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="6"/>
-      <c r="B262" s="7"/>
-      <c r="C262" s="7"/>
+      <c t="s" r="A262" s="6">
+        <v>13</v>
+      </c>
+      <c r="B262" s="7">
+        <v>813</v>
+      </c>
+      <c t="s" r="C262" s="7">
+        <v>14</v>
+      </c>
       <c r="D262" s="7"/>
-      <c r="E262" s="7"/>
-      <c r="F262" s="7"/>
-      <c r="G262" s="8"/>
-      <c r="H262" s="8"/>
-      <c r="I262" s="7"/>
-      <c r="J262" s="7"/>
+      <c t="s" r="E262" s="7">
+        <v>323</v>
+      </c>
+      <c r="F262" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G262" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H262" s="8">
+        <v>190</v>
+      </c>
+      <c t="s" r="I262" s="7">
+        <v>41</v>
+      </c>
+      <c t="s" r="J262" s="7">
+        <v>312</v>
+      </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
-      <c r="M262" s="7"/>
+      <c t="s" r="M262" s="7">
+        <v>324</v>
+      </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
       <c t="s" r="A263" s="6">
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>813</v>
+        <v>970</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>312</v>
+        <v>191</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9575,29 +9590,29 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>970</v>
+        <v>889</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9608,88 +9623,90 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
+        <v>190</v>
+      </c>
+      <c t="s" r="H265" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H265" s="8">
-        <v>188</v>
-      </c>
       <c t="s" r="I265" s="7">
-        <v>22</v>
+        <v>288</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>137</v>
+        <v>325</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c r="M265" s="7"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
-      <c t="s" r="A266" s="6">
-        <v>13</v>
-      </c>
-      <c r="B266" s="7">
-        <v>890</v>
-      </c>
-      <c t="s" r="C266" s="7">
-        <v>14</v>
-      </c>
+      <c r="A266" s="6"/>
+      <c r="B266" s="7"/>
+      <c r="C266" s="7"/>
       <c r="D266" s="7"/>
-      <c t="s" r="E266" s="7">
-        <v>324</v>
-      </c>
-      <c r="F266" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G266" s="8">
-        <v>188</v>
-      </c>
-      <c t="s" r="H266" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="I266" s="7">
-        <v>289</v>
-      </c>
-      <c t="s" r="J266" s="7">
-        <v>325</v>
-      </c>
+      <c r="E266" s="7"/>
+      <c r="F266" s="7"/>
+      <c r="G266" s="8"/>
+      <c r="H266" s="8"/>
+      <c r="I266" s="7"/>
+      <c r="J266" s="7"/>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="6"/>
-      <c r="B267" s="7"/>
-      <c r="C267" s="7"/>
+      <c t="s" r="A267" s="6">
+        <v>13</v>
+      </c>
+      <c r="B267" s="7">
+        <v>963</v>
+      </c>
+      <c t="s" r="C267" s="7">
+        <v>14</v>
+      </c>
       <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
-      <c r="F267" s="7"/>
-      <c r="G267" s="8"/>
-      <c r="H267" s="8"/>
-      <c r="I267" s="7"/>
-      <c r="J267" s="7"/>
+      <c t="s" r="E267" s="7">
+        <v>326</v>
+      </c>
+      <c r="F267" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G267" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H267" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I267" s="7">
+        <v>327</v>
+      </c>
+      <c t="s" r="J267" s="7">
+        <v>178</v>
+      </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
-      <c r="M267" s="7"/>
+      <c t="s" r="M267" s="7">
+        <v>328</v>
+      </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
       <c t="s" r="A268" s="6">
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>963</v>
+        <v>901</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
@@ -9702,29 +9719,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>31</v>
+        <v>238</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
-      <c t="s" r="M268" s="7">
-        <v>328</v>
-      </c>
+      <c r="M268" s="7"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c t="s" r="A269" s="6">
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
@@ -9737,16 +9752,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
+        <v>238</v>
+      </c>
+      <c t="s" r="H269" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H269" s="8">
-        <v>236</v>
-      </c>
       <c t="s" r="I269" s="7">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9757,7 +9772,7 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>902</v>
+        <v>465</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
@@ -9770,16 +9785,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>236</v>
+        <v>31</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9790,7 +9805,7 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
@@ -9803,65 +9818,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
+        <v>122</v>
+      </c>
+      <c t="s" r="H271" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H271" s="8">
-        <v>122</v>
-      </c>
       <c t="s" r="I271" s="7">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>105</v>
+        <v>252</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c r="M271" s="7"/>
     </row>
     <row r="272" ht="14.25" customHeight="1">
-      <c t="s" r="A272" s="6">
-        <v>13</v>
-      </c>
-      <c r="B272" s="7">
-        <v>466</v>
-      </c>
-      <c t="s" r="C272" s="7">
-        <v>14</v>
-      </c>
+      <c r="A272" s="6"/>
+      <c r="B272" s="7"/>
+      <c r="C272" s="7"/>
       <c r="D272" s="7"/>
-      <c t="s" r="E272" s="7">
-        <v>326</v>
-      </c>
-      <c r="F272" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G272" s="8">
-        <v>122</v>
-      </c>
-      <c t="s" r="H272" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I272" s="7">
-        <v>313</v>
-      </c>
-      <c t="s" r="J272" s="7">
-        <v>329</v>
-      </c>
+      <c r="E272" s="7"/>
+      <c r="F272" s="7"/>
+      <c r="G272" s="8"/>
+      <c r="H272" s="8"/>
+      <c r="I272" s="7"/>
+      <c r="J272" s="7"/>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c r="M272" s="7"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="6"/>
-      <c r="B273" s="7"/>
-      <c r="C273" s="7"/>
+      <c t="s" r="A273" s="6">
+        <v>13</v>
+      </c>
+      <c r="B273" s="7">
+        <v>628</v>
+      </c>
+      <c t="s" r="C273" s="7">
+        <v>14</v>
+      </c>
       <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
-      <c r="F273" s="7"/>
-      <c r="G273" s="8"/>
-      <c r="H273" s="8"/>
-      <c r="I273" s="7"/>
-      <c r="J273" s="7"/>
+      <c t="s" r="E273" s="7">
+        <v>329</v>
+      </c>
+      <c r="F273" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G273" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H273" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I273" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="J273" s="7">
+        <v>331</v>
+      </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7"/>
@@ -9871,29 +9886,29 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>331</v>
+        <v>178</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9904,29 +9919,29 @@
         <v>13</v>
       </c>
       <c r="B275" s="7">
-        <v>627</v>
+        <v>335</v>
       </c>
       <c t="s" r="C275" s="7">
         <v>14</v>
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9937,29 +9952,29 @@
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9970,29 +9985,29 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>338</v>
+        <v>144</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10003,29 +10018,29 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>254</v>
+        <v>519</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10036,29 +10051,29 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>255</v>
+        <v>522</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>252</v>
+        <v>114</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10171,10 +10186,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>249</v>
+        <v>335</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10204,7 +10219,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>53</v>
@@ -10234,7 +10249,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>146</v>
@@ -10264,7 +10279,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>31</v>
@@ -10273,7 +10288,7 @@
         <v>297</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10300,10 +10315,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>315</v>
@@ -10330,7 +10345,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>31</v>
@@ -10339,7 +10354,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10372,7 +10387,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10384,7 +10399,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>159</v>
@@ -10392,7 +10407,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10407,7 +10422,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10440,7 +10455,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10452,7 +10467,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>293</v>
@@ -10473,7 +10488,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10506,7 +10521,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10521,7 +10536,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10539,7 +10554,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10551,7 +10566,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>137</v>
@@ -10572,7 +10587,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10584,7 +10599,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>174</v>
@@ -10605,7 +10620,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10620,7 +10635,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10653,7 +10668,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10662,13 +10677,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10686,22 +10701,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10719,7 +10734,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10728,7 +10743,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>127</v>
@@ -10752,22 +10767,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10793,14 +10808,14 @@
         <v>13</v>
       </c>
       <c r="B304" s="7">
-        <v>130</v>
+        <v>306</v>
       </c>
       <c t="s" r="C304" s="7">
         <v>14</v>
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10809,13 +10824,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>33</v>
+        <v>335</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10826,29 +10841,29 @@
         <v>13</v>
       </c>
       <c r="B305" s="7">
-        <v>775</v>
+        <v>305</v>
       </c>
       <c t="s" r="C305" s="7">
         <v>14</v>
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>123</v>
+        <v>232</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>322</v>
+        <v>244</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10859,78 +10874,78 @@
         <v>13</v>
       </c>
       <c r="B306" s="7">
-        <v>1601</v>
+        <v>254</v>
       </c>
       <c t="s" r="C306" s="7">
         <v>14</v>
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>329</v>
+        <v>216</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c r="M306" s="7"/>
     </row>
     <row r="307" ht="14.25" customHeight="1">
-      <c r="A307" s="6"/>
-      <c r="B307" s="7"/>
-      <c r="C307" s="7"/>
+      <c t="s" r="A307" s="6">
+        <v>13</v>
+      </c>
+      <c r="B307" s="7">
+        <v>255</v>
+      </c>
+      <c t="s" r="C307" s="7">
+        <v>14</v>
+      </c>
       <c r="D307" s="7"/>
-      <c r="E307" s="7"/>
-      <c r="F307" s="7"/>
-      <c r="G307" s="8"/>
-      <c r="H307" s="8"/>
-      <c r="I307" s="7"/>
-      <c r="J307" s="7"/>
+      <c t="s" r="E307" s="7">
+        <v>346</v>
+      </c>
+      <c r="F307" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G307" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="H307" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I307" s="7">
+        <v>347</v>
+      </c>
+      <c t="s" r="J307" s="7">
+        <v>225</v>
+      </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c r="M307" s="7"/>
     </row>
     <row r="308" ht="14.25" customHeight="1">
-      <c t="s" r="A308" s="6">
-        <v>13</v>
-      </c>
-      <c r="B308" s="7">
-        <v>401</v>
-      </c>
-      <c t="s" r="C308" s="7">
-        <v>14</v>
-      </c>
+      <c r="A308" s="6"/>
+      <c r="B308" s="7"/>
+      <c r="C308" s="7"/>
       <c r="D308" s="7"/>
-      <c t="s" r="E308" s="7">
-        <v>346</v>
-      </c>
-      <c r="F308" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G308" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H308" s="8">
-        <v>69</v>
-      </c>
-      <c t="s" r="I308" s="7">
-        <v>262</v>
-      </c>
-      <c t="s" r="J308" s="7">
-        <v>160</v>
-      </c>
+      <c r="E308" s="7"/>
+      <c r="F308" s="7"/>
+      <c r="G308" s="8"/>
+      <c r="H308" s="8"/>
+      <c r="I308" s="7"/>
+      <c r="J308" s="7"/>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c r="M308" s="7"/>
@@ -10940,62 +10955,64 @@
         <v>13</v>
       </c>
       <c r="B309" s="7">
-        <v>798</v>
+        <v>401</v>
       </c>
       <c t="s" r="C309" s="7">
         <v>14</v>
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H309" s="8">
         <v>69</v>
       </c>
-      <c t="s" r="H309" s="8">
-        <v>131</v>
-      </c>
       <c t="s" r="I309" s="7">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
-      <c r="M309" s="7"/>
+      <c t="s" r="M309" s="7">
+        <v>349</v>
+      </c>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c t="s" r="A310" s="6">
         <v>13</v>
       </c>
       <c r="B310" s="7">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c t="s" r="C310" s="7">
         <v>14</v>
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
+        <v>69</v>
+      </c>
+      <c t="s" r="H310" s="8">
         <v>131</v>
       </c>
-      <c t="s" r="H310" s="8">
-        <v>69</v>
-      </c>
       <c t="s" r="I310" s="7">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11006,29 +11023,29 @@
         <v>13</v>
       </c>
       <c r="B311" s="7">
-        <v>402</v>
+        <v>799</v>
       </c>
       <c t="s" r="C311" s="7">
         <v>14</v>
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
+        <v>131</v>
+      </c>
+      <c t="s" r="H311" s="8">
         <v>69</v>
       </c>
-      <c t="s" r="H311" s="8">
-        <v>31</v>
-      </c>
       <c t="s" r="I311" s="7">
-        <v>322</v>
+        <v>91</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11039,29 +11056,29 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>1511</v>
+        <v>402</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
+        <v>69</v>
+      </c>
+      <c t="s" r="H312" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H312" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I312" s="7">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>74</v>
+        <v>199</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11072,29 +11089,29 @@
         <v>13</v>
       </c>
       <c r="B313" s="7">
-        <v>1518</v>
+        <v>1511</v>
       </c>
       <c t="s" r="C313" s="7">
         <v>14</v>
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H313" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H313" s="8">
-        <v>31</v>
-      </c>
       <c t="s" r="I313" s="7">
-        <v>182</v>
+        <v>277</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>290</v>
+        <v>74</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11105,29 +11122,29 @@
         <v>13</v>
       </c>
       <c r="B314" s="7">
-        <v>7238</v>
+        <v>1518</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H314" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H314" s="8">
-        <v>55</v>
-      </c>
       <c t="s" r="I314" s="7">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>347</v>
+        <v>289</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11135,148 +11152,148 @@
     </row>
     <row r="315" ht="15" customHeight="1">
       <c t="s" r="A315" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B315" s="7">
-        <v>7239</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C315" s="7">
         <v>14</v>
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H315" s="8">
         <v>55</v>
       </c>
-      <c t="s" r="H315" s="8">
-        <v>31</v>
-      </c>
       <c t="s" r="I315" s="7">
-        <v>348</v>
+        <v>114</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
     </row>
     <row r="316" ht="14.25" customHeight="1">
-      <c r="A316" s="6"/>
-      <c r="B316" s="7"/>
-      <c r="C316" s="7"/>
+      <c t="s" r="A316" s="6">
+        <v>26</v>
+      </c>
+      <c r="B316" s="7">
+        <v>7239</v>
+      </c>
+      <c t="s" r="C316" s="7">
+        <v>14</v>
+      </c>
       <c r="D316" s="7"/>
-      <c r="E316" s="7"/>
-      <c r="F316" s="7"/>
-      <c r="G316" s="8"/>
-      <c r="H316" s="8"/>
-      <c r="I316" s="7"/>
-      <c r="J316" s="7"/>
+      <c t="s" r="E316" s="7">
+        <v>348</v>
+      </c>
+      <c r="F316" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G316" s="8">
+        <v>55</v>
+      </c>
+      <c t="s" r="H316" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I316" s="7">
+        <v>351</v>
+      </c>
+      <c t="s" r="J316" s="7">
+        <v>352</v>
+      </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c r="M316" s="7"/>
     </row>
     <row r="317" ht="14.25" customHeight="1">
-      <c t="s" r="A317" s="6">
-        <v>13</v>
-      </c>
-      <c r="B317" s="7">
-        <v>120</v>
-      </c>
-      <c t="s" r="C317" s="7">
-        <v>14</v>
-      </c>
+      <c r="A317" s="6"/>
+      <c r="B317" s="7"/>
+      <c r="C317" s="7"/>
       <c r="D317" s="7"/>
-      <c t="s" r="E317" s="7">
-        <v>350</v>
-      </c>
-      <c r="F317" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G317" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H317" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I317" s="7">
-        <v>338</v>
-      </c>
-      <c t="s" r="J317" s="7">
-        <v>41</v>
-      </c>
+      <c r="E317" s="7"/>
+      <c r="F317" s="7"/>
+      <c r="G317" s="8"/>
+      <c r="H317" s="8"/>
+      <c r="I317" s="7"/>
+      <c r="J317" s="7"/>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
-      <c t="s" r="M317" s="7">
-        <v>351</v>
-      </c>
+      <c r="M317" s="7"/>
     </row>
     <row r="318" ht="14.25" customHeight="1">
       <c t="s" r="A318" s="6">
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H318" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H318" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I318" s="7">
-        <v>150</v>
+        <v>339</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>354</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c t="s" r="A319" s="6">
         <v>13</v>
       </c>
       <c r="B319" s="7">
-        <v>887</v>
+        <v>127</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11287,29 +11304,29 @@
         <v>13</v>
       </c>
       <c r="B320" s="7">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c t="s" r="C320" s="7">
         <v>14</v>
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11320,29 +11337,29 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>150</v>
+        <v>882</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>54</v>
+        <v>199</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11353,145 +11370,145 @@
         <v>13</v>
       </c>
       <c r="B322" s="7">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c t="s" r="C322" s="7">
         <v>14</v>
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H322" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H322" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I322" s="7">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>352</v>
+        <v>84</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c r="M322" s="7"/>
     </row>
     <row r="323" ht="14.25" customHeight="1">
-      <c r="A323" s="6"/>
-      <c r="B323" s="7"/>
-      <c r="C323" s="7"/>
+      <c t="s" r="A323" s="6">
+        <v>13</v>
+      </c>
+      <c r="B323" s="7">
+        <v>167</v>
+      </c>
+      <c t="s" r="C323" s="7">
+        <v>14</v>
+      </c>
       <c r="D323" s="7"/>
-      <c r="E323" s="7"/>
-      <c r="F323" s="7"/>
-      <c r="G323" s="8"/>
-      <c r="H323" s="8"/>
-      <c r="I323" s="7"/>
-      <c r="J323" s="7"/>
+      <c t="s" r="E323" s="7">
+        <v>353</v>
+      </c>
+      <c r="F323" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G323" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H323" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I323" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J323" s="7">
+        <v>355</v>
+      </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c r="M323" s="7"/>
     </row>
     <row r="324" ht="14.25" customHeight="1">
-      <c t="s" r="A324" s="6">
-        <v>13</v>
-      </c>
-      <c r="B324" s="7">
-        <v>302</v>
-      </c>
-      <c t="s" r="C324" s="7">
-        <v>14</v>
-      </c>
+      <c r="A324" s="6"/>
+      <c r="B324" s="7"/>
+      <c r="C324" s="7"/>
       <c r="D324" s="7"/>
-      <c t="s" r="E324" s="7">
-        <v>353</v>
-      </c>
-      <c r="F324" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G324" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H324" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="I324" s="7">
-        <v>142</v>
-      </c>
-      <c t="s" r="J324" s="7">
-        <v>157</v>
-      </c>
+      <c r="E324" s="7"/>
+      <c r="F324" s="7"/>
+      <c r="G324" s="8"/>
+      <c r="H324" s="8"/>
+      <c r="I324" s="7"/>
+      <c r="J324" s="7"/>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
-      <c t="s" r="M324" s="7">
-        <v>354</v>
-      </c>
+      <c r="M324" s="7"/>
     </row>
     <row r="325" ht="15" customHeight="1">
       <c t="s" r="A325" s="6">
         <v>13</v>
       </c>
       <c r="B325" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="C325" s="7">
         <v>14</v>
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H325" s="8">
         <v>92</v>
       </c>
-      <c t="s" r="H325" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I325" s="7">
-        <v>355</v>
+        <v>142</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
-      <c r="M325" s="7"/>
+      <c t="s" r="M325" s="7">
+        <v>357</v>
+      </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
       <c t="s" r="A326" s="6">
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>372</v>
+        <v>301</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>293</v>
+        <v>160</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11502,29 +11519,29 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>47</v>
+        <v>359</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>49</v>
+        <v>293</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11535,29 +11552,29 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>138</v>
+        <v>373</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>47</v>
+        <v>359</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>207</v>
+        <v>61</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>305</v>
+        <v>49</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11568,29 +11585,29 @@
         <v>13</v>
       </c>
       <c r="B329" s="7">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c t="s" r="C329" s="7">
         <v>14</v>
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H329" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H329" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I329" s="7">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>74</v>
+        <v>305</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11601,29 +11618,29 @@
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>376</v>
+        <v>147</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>182</v>
+        <v>308</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>290</v>
+        <v>74</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11634,145 +11651,145 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>47</v>
+        <v>359</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>218</v>
+        <v>289</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c r="M331" s="7"/>
     </row>
     <row r="332" ht="14.25" customHeight="1">
-      <c r="A332" s="6"/>
-      <c r="B332" s="7"/>
-      <c r="C332" s="7"/>
+      <c t="s" r="A332" s="6">
+        <v>13</v>
+      </c>
+      <c r="B332" s="7">
+        <v>377</v>
+      </c>
+      <c t="s" r="C332" s="7">
+        <v>14</v>
+      </c>
       <c r="D332" s="7"/>
-      <c r="E332" s="7"/>
-      <c r="F332" s="7"/>
-      <c r="G332" s="8"/>
-      <c r="H332" s="8"/>
-      <c r="I332" s="7"/>
-      <c r="J332" s="7"/>
+      <c t="s" r="E332" s="7">
+        <v>356</v>
+      </c>
+      <c r="F332" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G332" s="8">
+        <v>359</v>
+      </c>
+      <c t="s" r="H332" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I332" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="J332" s="7">
+        <v>220</v>
+      </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c r="M332" s="7"/>
     </row>
     <row r="333" ht="14.25" customHeight="1">
-      <c t="s" r="A333" s="6">
-        <v>13</v>
-      </c>
-      <c r="B333" s="7">
-        <v>121</v>
-      </c>
-      <c t="s" r="C333" s="7">
-        <v>14</v>
-      </c>
+      <c r="A333" s="6"/>
+      <c r="B333" s="7"/>
+      <c r="C333" s="7"/>
       <c r="D333" s="7"/>
-      <c t="s" r="E333" s="7">
-        <v>357</v>
-      </c>
-      <c r="F333" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G333" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H333" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I333" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="J333" s="7">
-        <v>150</v>
-      </c>
+      <c r="E333" s="7"/>
+      <c r="F333" s="7"/>
+      <c r="G333" s="8"/>
+      <c r="H333" s="8"/>
+      <c r="I333" s="7"/>
+      <c r="J333" s="7"/>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
-      <c t="s" r="M333" s="7">
-        <v>358</v>
-      </c>
+      <c r="M333" s="7"/>
     </row>
     <row r="334" ht="14.25" customHeight="1">
       <c t="s" r="A334" s="6">
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>825</v>
+        <v>121</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>359</v>
+        <v>47</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
-      <c r="M334" s="7"/>
+      <c t="s" r="M334" s="7">
+        <v>361</v>
+      </c>
     </row>
     <row r="335" ht="15" customHeight="1">
       <c t="s" r="A335" s="6">
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>359</v>
+        <v>47</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>47</v>
+        <v>362</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>322</v>
+        <v>68</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>360</v>
+        <v>205</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11783,29 +11800,29 @@
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>144</v>
+        <v>826</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>47</v>
+        <v>362</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11816,29 +11833,29 @@
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>519</v>
+        <v>876</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>96</v>
+        <v>364</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>76</v>
+        <v>365</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>266</v>
+        <v>347</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11849,29 +11866,29 @@
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>522</v>
+        <v>877</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>96</v>
+        <v>364</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11904,7 +11921,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11919,7 +11936,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11937,7 +11954,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11949,7 +11966,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>51</v>
@@ -11970,7 +11987,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11979,7 +11996,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>308</v>
@@ -12003,19 +12020,19 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>77</v>
@@ -12051,7 +12068,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12063,7 +12080,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>45</v>
@@ -12071,7 +12088,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12086,7 +12103,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12098,7 +12115,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>295</v>
@@ -12119,7 +12136,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12131,10 +12148,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12152,7 +12169,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12164,10 +12181,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12185,7 +12202,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12194,7 +12211,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>126</v>
@@ -12218,13 +12235,13 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>31</v>
@@ -12251,7 +12268,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12263,7 +12280,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>132</v>
@@ -12299,7 +12316,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12332,7 +12349,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12344,7 +12361,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>127</v>
@@ -12365,7 +12382,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12377,7 +12394,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>97</v>
@@ -12398,7 +12415,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12410,10 +12427,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12431,7 +12448,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12479,7 +12496,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12512,7 +12529,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12545,7 +12562,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12557,10 +12574,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12578,7 +12595,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12593,7 +12610,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12611,7 +12628,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12623,7 +12640,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>94</v>
@@ -12644,7 +12661,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12659,7 +12676,7 @@
         <v>297</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12677,7 +12694,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12689,10 +12706,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12725,7 +12742,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12734,10 +12751,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>19</v>
@@ -12758,19 +12775,19 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>61</v>
@@ -12791,7 +12808,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12824,7 +12841,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -12839,7 +12856,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12857,7 +12874,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12866,10 +12883,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>156</v>
@@ -12890,13 +12907,13 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>47</v>
@@ -12905,7 +12922,7 @@
         <v>291</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12938,7 +12955,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12950,10 +12967,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12971,7 +12988,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12980,7 +12997,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>63</v>
@@ -13004,13 +13021,13 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
@@ -13052,7 +13069,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13061,13 +13078,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13085,13 +13102,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>31</v>
@@ -13100,7 +13117,7 @@
         <v>173</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13133,7 +13150,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13145,7 +13162,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>334</v>
@@ -13168,7 +13185,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13183,7 +13200,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13201,7 +13218,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13213,7 +13230,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>124</v>
@@ -13234,7 +13251,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13249,7 +13266,7 @@
         <v>307</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13267,7 +13284,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13279,10 +13296,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13300,7 +13317,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13333,7 +13350,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13348,7 +13365,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13381,7 +13398,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13390,10 +13407,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>18</v>
@@ -13401,7 +13418,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13416,13 +13433,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>47</v>
@@ -13431,7 +13448,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13449,7 +13466,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13482,7 +13499,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13494,7 +13511,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>134</v>
@@ -13515,7 +13532,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13524,7 +13541,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>179</v>
@@ -13548,13 +13565,13 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>47</v>
@@ -13563,7 +13580,7 @@
         <v>296</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13581,7 +13598,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13614,7 +13631,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13623,10 +13640,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>68</v>
@@ -13662,7 +13679,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13677,7 +13694,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13695,7 +13712,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13704,7 +13721,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>63</v>
@@ -13728,19 +13745,19 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>252</v>
+        <v>347</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>98</v>
@@ -13761,7 +13778,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13770,7 +13787,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>299</v>
@@ -13794,22 +13811,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13842,7 +13859,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13851,7 +13868,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c t="s" r="I404" s="7">
         <v>65</v>
@@ -13877,19 +13894,19 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>68</v>
@@ -13910,7 +13927,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13919,10 +13936,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>51</v>
@@ -13943,13 +13960,13 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>47</v>
@@ -13976,7 +13993,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13985,13 +14002,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14009,13 +14026,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>47</v>
@@ -14057,7 +14074,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14090,7 +14107,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14102,10 +14119,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>249</v>
+        <v>335</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14123,7 +14140,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14138,7 +14155,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14156,7 +14173,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14168,7 +14185,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>75</v>
@@ -14204,7 +14221,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14224,7 +14241,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14239,7 +14256,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14272,7 +14289,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14287,7 +14304,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14305,7 +14322,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14317,7 +14334,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>72</v>
@@ -14353,7 +14370,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14365,15 +14382,15 @@
         <v>96</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -14388,7 +14405,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14408,7 +14425,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>393</v>
+        <v>170</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -14423,7 +14440,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14456,7 +14473,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14468,10 +14485,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14489,7 +14506,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14498,7 +14515,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>124</v>
@@ -14522,13 +14539,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>47</v>
@@ -14537,7 +14554,7 @@
         <v>308</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14570,7 +14587,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14579,10 +14596,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>143</v>
@@ -14605,13 +14622,13 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>31</v>
@@ -14638,7 +14655,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -14671,7 +14688,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -14686,7 +14703,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14704,7 +14721,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -14737,7 +14754,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -14770,7 +14787,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
@@ -14803,7 +14820,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
@@ -14815,7 +14832,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>106</v>
@@ -14851,7 +14868,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -14860,13 +14877,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>169</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14884,13 +14901,13 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>47</v>
@@ -14917,7 +14934,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14929,10 +14946,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14950,7 +14967,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -14998,7 +15015,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15010,7 +15027,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>111</v>
@@ -15018,7 +15035,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -15033,7 +15050,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15066,7 +15083,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15081,7 +15098,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15114,7 +15131,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15134,7 +15151,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15149,7 +15166,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15164,7 +15181,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15182,7 +15199,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15197,7 +15214,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15215,7 +15232,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15224,10 +15241,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>147</v>
@@ -15248,13 +15265,13 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>47</v>
@@ -15263,7 +15280,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15281,7 +15298,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15314,7 +15331,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -15326,10 +15343,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15362,7 +15379,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15382,7 +15399,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -15397,7 +15414,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -15406,10 +15423,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>126</v>
@@ -15430,13 +15447,13 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>17</v>
@@ -15445,7 +15462,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15478,7 +15495,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15526,13 +15543,13 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>47</v>
@@ -15541,7 +15558,7 @@
         <v>312</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15559,7 +15576,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
@@ -15574,7 +15591,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15603,11 +15620,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C463" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -15616,13 +15633,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c t="s" r="I463" s="7">
         <v>169</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15636,17 +15653,17 @@
         <v>5806</v>
       </c>
       <c t="s" r="C464" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>17</v>
@@ -15655,7 +15672,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15688,7 +15705,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -15721,7 +15738,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
@@ -15730,13 +15747,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="I467" s="7">
         <v>105</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -15769,7 +15786,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -15802,7 +15819,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -15811,13 +15828,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c t="s" r="I470" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15835,13 +15852,13 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>47</v>
@@ -15850,7 +15867,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -15883,7 +15900,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
@@ -15892,13 +15909,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c t="s" r="I473" s="7">
         <v>312</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -15916,22 +15933,22 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G474" s="8">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c t="s" r="H474" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -15939,7 +15956,7 @@
     </row>
     <row r="475" ht="16.5" customHeight="1">
       <c t="s" r="A475" s="9">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B475" s="9"/>
       <c r="C475" s="9"/>
@@ -15959,7 +15976,7 @@
     <row r="476" ht="65.25" customHeight="1"/>
     <row r="477" ht="16.5" customHeight="1">
       <c t="s" r="A477" s="10">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B477" s="10"/>
       <c r="C477" s="10"/>
@@ -15972,7 +15989,7 @@
       <c r="J477" s="10"/>
       <c r="K477" s="10"/>
       <c t="s" r="L477" s="11">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M477" s="11"/>
       <c r="N477" s="11"/>
